--- a/restoration-calculator/templates/seisan_template.xlsx
+++ b/restoration-calculator/templates/seisan_template.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="退去精算書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'退去精算書'!$9:$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -452,17 +454,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,5 +552,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>